--- a/exam_forms/006_parasympatholytics_knowledge_quiz--exam_forms.xlsx
+++ b/exam_forms/006_parasympatholytics_knowledge_quiz--exam_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>drug_name</t>
+          <t>What is the name of the drug you are referring to?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>drug_name</t>
+          <t>drug_dosage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>drug_name</t>
+          <t>How much of the drug were you given?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,58 +589,58 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dosage</t>
+          <t>drug_unit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dosage</t>
+          <t>In what unit are the drug measurements?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dosage_unit</t>
+          <t>drug_class</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dosage_unit</t>
+          <t>What is the drug class?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>drug_class</t>
+          <t>side_effects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>drug_class</t>
+          <t>What are the side effects you experienced?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>correct_answer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>What is your correct answer?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>drug_class</t>
+          <t>event_date_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>drug_class</t>
+          <t>What is the date and time of the event?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>drug_type</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>drug_type</t>
+          <t>What is the time of the event?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>Do you have any additional note?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,343 +745,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>What is your contact email?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date_time</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date_time</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>time_unit</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>time_unit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1211,168 +912,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drug_class_choices</t>
+          <t>correct_answer_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>a1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>drug_class_choices</t>
+          <t>correct_answer_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>drug_class_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>a3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>drug_type_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>drug_type_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>drug_type_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>correct_answer_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
